--- a/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_SKALA USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_SKALA USAHA.xlsx
@@ -693,13 +693,13 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -723,16 +723,16 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Y2" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Z2" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="AA2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK2" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AL2" t="n">
         <v>384</v>
@@ -833,19 +833,19 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="O3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -857,31 +857,31 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Y3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="Z3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="AA3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -893,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AK3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="AL3" t="n">
         <v>354</v>
@@ -973,10 +973,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="O4" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -997,31 +997,31 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="Y4" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="Z4" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="AA4" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="AB4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1033,16 +1033,16 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AK4" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="AL4" t="n">
         <v>336</v>
@@ -1113,13 +1113,13 @@
         <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="O5" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1143,19 +1143,19 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Y5" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="Z5" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AK5" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AL5" t="n">
         <v>288</v>
@@ -1253,22 +1253,22 @@
         <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="O6" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1283,28 +1283,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Y6" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="Z6" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="AA6" t="n">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="AB6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AK6" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="AL6" t="n">
         <v>303</v>
@@ -1525,19 +1525,19 @@
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1549,31 +1549,31 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Y8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1591,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL8" t="n">
         <v>324</v>
@@ -1668,19 +1668,19 @@
         <v>238</v>
       </c>
       <c r="O9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="P9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1695,28 +1695,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Y9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Z9" t="n">
         <v>238</v>
       </c>
       <c r="AA9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1731,10 +1731,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AK9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AL9" t="n">
         <v>379</v>
@@ -1805,19 +1805,19 @@
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="O10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1835,25 +1835,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Y10" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="Z10" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AA10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1871,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AK10" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AL10" t="n">
         <v>373</v>
@@ -1945,13 +1945,13 @@
         <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="O11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1969,25 +1969,25 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Y11" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="Z11" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AA11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2005,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <v>435</v>
       </c>
       <c r="AK11" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AL11" t="n">
         <v>383</v>
@@ -2085,16 +2085,16 @@
         <v>7</v>
       </c>
       <c r="N12" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="O12" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2115,25 +2115,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="Y12" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="Z12" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="AA12" t="n">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="AB12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AK12" t="n">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="AL12" t="n">
         <v>373</v>
@@ -2225,19 +2225,19 @@
         <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="O13" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2249,31 +2249,31 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y13" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="Z13" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AA13" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2285,16 +2285,16 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AK13" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AL13" t="n">
         <v>364</v>
@@ -2365,19 +2365,19 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="O14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2395,25 +2395,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Y14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="Z14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="AA14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="AB14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2431,10 +2431,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AK14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="n">
         <v>359</v>
@@ -2505,16 +2505,16 @@
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O15" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2538,19 +2538,19 @@
         <v>398</v>
       </c>
       <c r="Y15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AA15" t="n">
         <v>161</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         <v>398</v>
       </c>
       <c r="AK15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AL15" t="n">
         <v>367</v>
@@ -2645,22 +2645,22 @@
         <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="O16" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
         <v>6</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2669,34 +2669,34 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="Y16" t="n">
+        <v>246</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>192</v>
+      </c>
+      <c r="AA16" t="n">
         <v>226</v>
       </c>
-      <c r="Z16" t="n">
-        <v>213</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>215</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
         <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2705,16 +2705,16 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AK16" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="AL16" t="n">
         <v>370</v>
@@ -2785,19 +2785,19 @@
         <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="O17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="P17" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2815,25 +2815,25 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Y17" t="n">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="AA17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AB17" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2851,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AK17" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="AL17" t="n">
         <v>366</v>
@@ -2925,16 +2925,16 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="O18" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2949,25 +2949,25 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Y18" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="Z18" t="n">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="AA18" t="n">
         <v>170</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2985,16 +2985,16 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK18" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="AL18" t="n">
         <v>423</v>
@@ -3065,16 +3065,16 @@
         <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="O19" t="n">
         <v>227</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="Y19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="Z19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AA19" t="n">
         <v>227</v>
       </c>
       <c r="AB19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3125,16 +3125,16 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AK19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AL19" t="n">
         <v>371</v>
@@ -3205,13 +3205,13 @@
         <v>20</v>
       </c>
       <c r="N20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
         <v>217</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3238,16 +3238,16 @@
         <v>298</v>
       </c>
       <c r="Y20" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="Z20" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="AA20" t="n">
         <v>217</v>
       </c>
       <c r="AB20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>298</v>
       </c>
       <c r="AK20" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AL20" t="n">
         <v>284</v>
@@ -3345,13 +3345,13 @@
         <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O21" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3378,16 +3378,16 @@
         <v>401</v>
       </c>
       <c r="Y21" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA21" t="n">
         <v>177</v>
       </c>
-      <c r="Z21" t="n">
-        <v>224</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>165</v>
-      </c>
       <c r="AB21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>401</v>
       </c>
       <c r="AK21" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AL21" t="n">
         <v>367</v>
@@ -3485,19 +3485,19 @@
         <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="O22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="P22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -3515,25 +3515,25 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="Y22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="Z22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="AA22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="AB22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="AK22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="AL22" t="n">
         <v>450</v>
@@ -3625,19 +3625,19 @@
         <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="O23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="P23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -3655,25 +3655,25 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Y23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="Z23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AA23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AB23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3691,10 +3691,10 @@
         <v>1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AK23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AL23" t="n">
         <v>308</v>
@@ -3765,19 +3765,19 @@
         <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="O24" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="P24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3795,26 +3795,26 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="Y24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="Z24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="AA24" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AB24" t="n">
         <v>25</v>
       </c>
       <c r="AC24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD24" t="n">
         <v>3</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
@@ -3831,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="AK24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="AL24" t="n">
         <v>386</v>
@@ -3905,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="O25" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -3935,25 +3935,25 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Z25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="AA25" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3971,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AL25" t="n">
         <v>396</v>
@@ -4045,19 +4045,19 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O26" t="n">
         <v>170</v>
       </c>
       <c r="P26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4075,25 +4075,25 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Y26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="Z26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="AA26" t="n">
         <v>170</v>
       </c>
       <c r="AB26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4111,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AK26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AL26" t="n">
         <v>282</v>
@@ -4185,13 +4185,13 @@
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="O27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4215,19 +4215,19 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Y27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="Z27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="AA27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="AB27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4251,10 +4251,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AK27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="AL27" t="n">
         <v>363</v>
@@ -4325,19 +4325,19 @@
         <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="O28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4349,31 +4349,31 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="Y28" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="Z28" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AA28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4385,16 +4385,16 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AK28" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="AL28" t="n">
         <v>384</v>
@@ -4465,19 +4465,19 @@
         <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="O29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4495,16 +4495,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Y29" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="Z29" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="AA29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4531,10 +4531,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AK29" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="AL29" t="n">
         <v>357</v>
@@ -4608,13 +4608,13 @@
         <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4635,22 +4635,22 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Y30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Z30" t="n">
         <v>10</v>
       </c>
       <c r="AA30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4671,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AK30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="n">
         <v>315</v>
@@ -4745,13 +4745,13 @@
         <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="O31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -4775,19 +4775,19 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Y31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="Z31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AA31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="AB31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4811,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AK31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AL31" t="n">
         <v>366</v>
@@ -4885,19 +4885,19 @@
         <v>9</v>
       </c>
       <c r="N32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="O32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -4909,31 +4909,31 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="Y32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="Z32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AA32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4945,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
         <v>1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AK32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AL32" t="n">
         <v>455</v>
@@ -5165,13 +5165,13 @@
         <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="O34" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5189,22 +5189,22 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Y34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="Z34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AA34" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5225,16 +5225,16 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AK34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AL34" t="n">
         <v>290</v>
@@ -5305,22 +5305,22 @@
         <v>20</v>
       </c>
       <c r="N35" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="O35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="P35" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -5335,22 +5335,22 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="Y35" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Z35" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="AA35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="AB35" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="AC35" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5371,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AK35" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AL35" t="n">
         <v>372</v>
@@ -5445,13 +5445,13 @@
         <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="O36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
         <v>2</v>
@@ -5478,16 +5478,16 @@
         <v>491</v>
       </c>
       <c r="Y36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="Z36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AA36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AB36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC36" t="n">
         <v>2</v>
@@ -5514,7 +5514,7 @@
         <v>491</v>
       </c>
       <c r="AK36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AL36" t="n">
         <v>453</v>
@@ -5585,19 +5585,19 @@
         <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="O37" t="n">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="P37" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -5615,26 +5615,26 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Y37" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="Z37" t="n">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="AA37" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="AB37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD37" t="n">
         <v>18</v>
       </c>
-      <c r="AC37" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>25</v>
-      </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
@@ -5651,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AK37" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="AL37" t="n">
         <v>445</v>
@@ -5725,19 +5725,19 @@
         <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="O38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -5755,19 +5755,19 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y38" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="Z38" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AA38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AB38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5791,10 +5791,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK38" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AL38" t="n">
         <v>379</v>
@@ -5865,19 +5865,19 @@
         <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="O39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -5889,31 +5889,31 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="Y39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="Z39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="AA39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AB39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AD39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -5925,16 +5925,16 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AK39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="AL39" t="n">
         <v>410</v>
@@ -6005,16 +6005,16 @@
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="O40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -6038,19 +6038,19 @@
         <v>395</v>
       </c>
       <c r="Y40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="Z40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="AA40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         <v>395</v>
       </c>
       <c r="AK40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AL40" t="n">
         <v>378</v>
@@ -6145,19 +6145,19 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="O41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -6175,25 +6175,25 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Y41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AA41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AB41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -6211,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AK41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AL41" t="n">
         <v>331</v>
@@ -6285,19 +6285,19 @@
         <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="O42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="P42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -6315,25 +6315,25 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Y42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="Z42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="AA42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="AB42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -6351,10 +6351,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AK42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AL42" t="n">
         <v>301</v>
@@ -6425,16 +6425,16 @@
         <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="P43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -6455,22 +6455,22 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="Y43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Z43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AA43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="AB43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AK43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AL43" t="n">
         <v>371</v>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>277</v>
+        <v>545</v>
       </c>
       <c r="O44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -6580,7 +6580,7 @@
         <v>15</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -6589,13 +6589,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>385</v>
+        <v>653</v>
       </c>
       <c r="Y44" t="n">
         <v>102</v>
@@ -6604,7 +6604,7 @@
         <v>277</v>
       </c>
       <c r="AA44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB44" t="n">
         <v>1</v>
@@ -6616,7 +6616,7 @@
         <v>15</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6705,31 +6705,31 @@
         <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="O45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="P45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -6738,34 +6738,34 @@
         <v>461</v>
       </c>
       <c r="Y45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="Z45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AA45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="AB45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6774,7 +6774,7 @@
         <v>461</v>
       </c>
       <c r="AK45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AL45" t="n">
         <v>434</v>
@@ -6845,16 +6845,16 @@
         <v>13</v>
       </c>
       <c r="N46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="O46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6878,19 +6878,19 @@
         <v>400</v>
       </c>
       <c r="Y46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Z46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="AA46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AB46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
         <v>400</v>
       </c>
       <c r="AK46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AL46" t="n">
         <v>375</v>
@@ -6985,13 +6985,13 @@
         <v>12</v>
       </c>
       <c r="N47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="O47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7018,16 +7018,16 @@
         <v>449</v>
       </c>
       <c r="Y47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="Z47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="AA47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AB47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
         <v>449</v>
       </c>
       <c r="AK47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AL47" t="n">
         <v>411</v>
@@ -7125,16 +7125,16 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="O48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="P48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -7155,22 +7155,22 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Y48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="Z48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="AA48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="AB48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -7191,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AK48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="AL48" t="n">
         <v>363</v>
@@ -7265,19 +7265,19 @@
         <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="O49" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -7295,25 +7295,25 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Y49" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="Z49" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="AA49" t="n">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="AB49" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -7331,10 +7331,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AK49" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AL49" t="n">
         <v>356</v>
@@ -7405,13 +7405,13 @@
         <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="O50" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -7423,31 +7423,31 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Y50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="Z50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA50" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="AB50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -7471,10 +7471,10 @@
         <v>1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AK50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AL50" t="n">
         <v>372</v>
@@ -7545,19 +7545,19 @@
         <v>9</v>
       </c>
       <c r="N51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="O51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -7575,25 +7575,25 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="Y51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="Z51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="AA51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AD51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -7611,10 +7611,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AK51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AL51" t="n">
         <v>395</v>
@@ -7685,19 +7685,19 @@
         <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="P52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -7709,31 +7709,31 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Y52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Z52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AA52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AB52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -7745,16 +7745,16 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AK52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AL52" t="n">
         <v>378</v>
@@ -7825,19 +7825,19 @@
         <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="O53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -7855,25 +7855,25 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="Y53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="Z53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="AA53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AD53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -7891,10 +7891,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="AK53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="AL53" t="n">
         <v>507</v>
@@ -7965,19 +7965,19 @@
         <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="O54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="P54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -7995,25 +7995,25 @@
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="Y54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="Z54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AA54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="AB54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -8031,10 +8031,10 @@
         <v>1</v>
       </c>
       <c r="AJ54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AK54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="AL54" t="n">
         <v>407</v>
@@ -8105,13 +8105,13 @@
         <v>5</v>
       </c>
       <c r="N55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O55" t="n">
         <v>156</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -8135,19 +8135,19 @@
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Y55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="Z55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AA55" t="n">
         <v>156</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -8171,10 +8171,10 @@
         <v>1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AK55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AL55" t="n">
         <v>308</v>
@@ -8245,13 +8245,13 @@
         <v>9</v>
       </c>
       <c r="N56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="O56" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="P56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -8275,28 +8275,28 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="Y56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="Z56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="AA56" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AB56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AK56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="AL56" t="n">
         <v>363</v>
@@ -8385,16 +8385,16 @@
         <v>14</v>
       </c>
       <c r="N57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="O57" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="P57" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="Y57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="Z57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AA57" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AB57" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AC57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8451,10 +8451,10 @@
         <v>1</v>
       </c>
       <c r="AJ57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AK57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AL57" t="n">
         <v>383</v>
@@ -8525,16 +8525,16 @@
         <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="O58" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="P58" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R58" t="n">
         <v>7</v>
@@ -8549,31 +8549,31 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W58" t="n">
         <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="Y58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="Z58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AA58" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AB58" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AC58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -8585,16 +8585,16 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AI58" t="n">
         <v>1</v>
       </c>
       <c r="AJ58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AK58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AL58" t="n">
         <v>419</v>
@@ -8665,16 +8665,16 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="O59" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="P59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8695,22 +8695,22 @@
         <v>1</v>
       </c>
       <c r="X59" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Y59" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="Z59" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="AA59" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8731,10 +8731,10 @@
         <v>1</v>
       </c>
       <c r="AJ59" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AK59" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AL59" t="n">
         <v>314</v>
@@ -8805,19 +8805,19 @@
         <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="O60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="P60" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -8835,25 +8835,25 @@
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="Y60" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z60" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="AA60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="AB60" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -8871,10 +8871,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AK60" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="AL60" t="n">
         <v>365</v>
@@ -8945,19 +8945,19 @@
         <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="O61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -8975,25 +8975,25 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Y61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="Z61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="AA61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="AB61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -9011,10 +9011,10 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AK61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AL61" t="n">
         <v>365</v>
@@ -9085,16 +9085,16 @@
         <v>14</v>
       </c>
       <c r="N62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="O62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="P62" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -9115,22 +9115,22 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="Y62" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="Z62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AA62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="AB62" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="AC62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -9151,10 +9151,10 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AK62" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AL62" t="n">
         <v>405</v>
@@ -9225,13 +9225,13 @@
         <v>18</v>
       </c>
       <c r="N63" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="O63" t="n">
         <v>191</v>
       </c>
       <c r="P63" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -9255,19 +9255,19 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Y63" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="Z63" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AA63" t="n">
         <v>191</v>
       </c>
       <c r="AB63" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -9291,10 +9291,10 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AK63" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AL63" t="n">
         <v>417</v>
@@ -9365,19 +9365,19 @@
         <v>10</v>
       </c>
       <c r="N64" t="n">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="O64" t="n">
         <v>164</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -9395,19 +9395,19 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Y64" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="Z64" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AA64" t="n">
         <v>164</v>
       </c>
       <c r="AB64" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -9431,10 +9431,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AK64" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AL64" t="n">
         <v>303</v>
@@ -9505,22 +9505,22 @@
         <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="O65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -9535,28 +9535,28 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Z65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="AA65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AB65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
         <v>0</v>
@@ -9571,10 +9571,10 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AK65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AL65" t="n">
         <v>373</v>
@@ -9645,16 +9645,16 @@
         <v>9</v>
       </c>
       <c r="N66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="P66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -9675,22 +9675,22 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Z66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AA66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AB66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AC66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AK66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AL66" t="n">
         <v>317</v>
@@ -9925,19 +9925,19 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="O68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -9955,25 +9955,25 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Y68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="Z68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="AA68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="AB68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -9991,10 +9991,10 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AK68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="AL68" t="n">
         <v>278</v>
@@ -10068,16 +10068,16 @@
         <v>239</v>
       </c>
       <c r="O69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" t="n">
         <v>1</v>
@@ -10104,16 +10104,16 @@
         <v>239</v>
       </c>
       <c r="AA69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AB69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -10125,7 +10125,7 @@
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI69" t="n">
         <v>1</v>
@@ -10205,19 +10205,19 @@
         <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="O70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -10235,25 +10235,25 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Y70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="Z70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AA70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AB70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AK70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AL70" t="n">
         <v>359</v>
@@ -10345,19 +10345,19 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="O71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="P71" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -10375,25 +10375,25 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Y71" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Z71" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="AB71" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE71" t="n">
         <v>0</v>
@@ -10411,10 +10411,10 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AK71" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AL71" t="n">
         <v>357</v>
@@ -10485,13 +10485,13 @@
         <v>6</v>
       </c>
       <c r="N72" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="O72" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="P72" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -10515,25 +10515,25 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Y72" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="Z72" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AA72" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="AB72" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -10551,10 +10551,10 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AK72" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AL72" t="n">
         <v>319</v>
@@ -10625,19 +10625,19 @@
         <v>7</v>
       </c>
       <c r="N73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="O73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="P73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -10655,25 +10655,25 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="Y73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="Z73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="AA73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="AB73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE73" t="n">
         <v>0</v>
@@ -10691,10 +10691,10 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AK73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="AL73" t="n">
         <v>350</v>
@@ -10765,16 +10765,16 @@
         <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="O74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="P74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -10795,22 +10795,22 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="Y74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="Z74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="AA74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AB74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10831,10 +10831,10 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="AK74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="AL74" t="n">
         <v>395</v>
@@ -10905,25 +10905,25 @@
         <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="O75" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -10935,31 +10935,31 @@
         <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Y75" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="Z75" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="AA75" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="AB75" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
         <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -10971,10 +10971,10 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AK75" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="AL75" t="n">
         <v>263</v>
@@ -11045,25 +11045,25 @@
         <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="O76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="P76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -11075,31 +11075,31 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Y76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="Z76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AA76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AB76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE76" t="n">
         <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -11111,10 +11111,10 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AK76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AL76" t="n">
         <v>342</v>
@@ -11185,10 +11185,10 @@
         <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="O77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -11197,13 +11197,13 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -11215,16 +11215,16 @@
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="Z77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="AA77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -11233,13 +11233,13 @@
         <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
         <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -11251,10 +11251,10 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AK77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="AL77" t="n">
         <v>313</v>
@@ -11325,13 +11325,13 @@
         <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="O78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="P78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -11349,25 +11349,25 @@
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W78" t="n">
         <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Y78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="Z78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="AA78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AB78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -11385,16 +11385,16 @@
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
       </c>
       <c r="AJ78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AK78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="AL78" t="n">
         <v>385</v>
@@ -11465,13 +11465,13 @@
         <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="O79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
@@ -11489,25 +11489,25 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="W79" t="n">
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Y79" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="Z79" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AA79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="AB79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="n">
         <v>1</v>
@@ -11525,16 +11525,16 @@
         <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AK79" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AL79" t="n">
         <v>419</v>
@@ -11605,13 +11605,13 @@
         <v>13</v>
       </c>
       <c r="N80" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O80" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="P80" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -11629,25 +11629,25 @@
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W80" t="n">
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Y80" t="n">
+        <v>206</v>
+      </c>
+      <c r="Z80" t="n">
         <v>199</v>
       </c>
-      <c r="Z80" t="n">
-        <v>201</v>
-      </c>
       <c r="AA80" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AB80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -11665,16 +11665,16 @@
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AK80" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AL80" t="n">
         <v>324</v>
@@ -11745,25 +11745,25 @@
         <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="O81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="P81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -11775,31 +11775,31 @@
         <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Y81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="Z81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="AA81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="AB81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AC81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AD81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -11811,10 +11811,10 @@
         <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AK81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="AL81" t="n">
         <v>378</v>
@@ -11885,13 +11885,13 @@
         <v>3</v>
       </c>
       <c r="N82" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="O82" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="P82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -11918,16 +11918,16 @@
         <v>383</v>
       </c>
       <c r="Y82" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="Z82" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AA82" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="AB82" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11951,10 +11951,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AK82" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AL82" t="n">
         <v>367</v>
@@ -12025,16 +12025,16 @@
         <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="O83" t="n">
         <v>125</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R83" t="n">
         <v>12</v>
@@ -12055,22 +12055,22 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Y83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="Z83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="AA83" t="n">
         <v>125</v>
       </c>
       <c r="AB83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD83" t="n">
         <v>12</v>
@@ -12091,10 +12091,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AK83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AL83" t="n">
         <v>360</v>
@@ -12165,19 +12165,19 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="O84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -12195,25 +12195,25 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="Y84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="Z84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="AA84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="AB84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -12231,10 +12231,10 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AK84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="AL84" t="n">
         <v>356</v>
@@ -12308,13 +12308,13 @@
         <v>146</v>
       </c>
       <c r="O85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -12338,19 +12338,19 @@
         <v>323</v>
       </c>
       <c r="Y85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Z85" t="n">
         <v>146</v>
       </c>
       <c r="AA85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AB85" t="n">
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>323</v>
       </c>
       <c r="AK85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AL85" t="n">
         <v>301</v>
@@ -12445,13 +12445,13 @@
         <v>4</v>
       </c>
       <c r="N86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="O86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="P86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -12469,7 +12469,7 @@
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -12478,16 +12478,16 @@
         <v>420</v>
       </c>
       <c r="Y86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="Z86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="AA86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AB86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>420</v>
       </c>
       <c r="AK86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AL86" t="n">
         <v>399</v>
@@ -12585,16 +12585,16 @@
         <v>10</v>
       </c>
       <c r="N87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="O87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="P87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -12609,28 +12609,28 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Y87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="Z87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AA87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="AB87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12645,16 +12645,16 @@
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AK87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AL87" t="n">
         <v>366</v>
@@ -12725,20 +12725,20 @@
         <v>8</v>
       </c>
       <c r="N88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="O88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
+        <v>9</v>
+      </c>
+      <c r="R88" t="n">
         <v>6</v>
       </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
       <c r="S88" t="n">
         <v>0</v>
       </c>
@@ -12749,32 +12749,32 @@
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" t="n">
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Y88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="Z88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AA88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AB88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD88" t="n">
         <v>6</v>
       </c>
-      <c r="AD88" t="n">
-        <v>1</v>
-      </c>
       <c r="AE88" t="n">
         <v>0</v>
       </c>
@@ -12785,16 +12785,16 @@
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AK88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AL88" t="n">
         <v>364</v>
@@ -12865,13 +12865,13 @@
         <v>2</v>
       </c>
       <c r="N89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="O89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -12889,25 +12889,25 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Y89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="Z89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="AA89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AB89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -12925,16 +12925,16 @@
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
       <c r="AJ89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AK89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="AL89" t="n">
         <v>440</v>
@@ -13005,13 +13005,13 @@
         <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="O90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="P90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W90" t="n">
         <v>0</v>
@@ -13038,16 +13038,16 @@
         <v>386</v>
       </c>
       <c r="Y90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AA90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="AB90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -13065,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -13074,7 +13074,7 @@
         <v>386</v>
       </c>
       <c r="AK90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AL90" t="n">
         <v>335</v>
@@ -13145,76 +13145,76 @@
         <v>5</v>
       </c>
       <c r="N91" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="O91" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q91" t="n">
         <v>4</v>
       </c>
       <c r="R91" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W91" t="n">
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="Y91" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="Z91" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AA91" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="AB91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC91" t="n">
         <v>4</v>
       </c>
       <c r="AD91" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AK91" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="AL91" t="n">
         <v>430</v>
@@ -13285,19 +13285,19 @@
         <v>6</v>
       </c>
       <c r="N92" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="O92" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -13315,25 +13315,25 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Y92" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="Z92" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AA92" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AB92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE92" t="n">
         <v>0</v>
@@ -13351,10 +13351,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AK92" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AL92" t="n">
         <v>343</v>
@@ -13425,19 +13425,19 @@
         <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="O93" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P93" t="n">
         <v>2</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -13455,25 +13455,25 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="Y93" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Z93" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="AA93" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AB93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -13491,10 +13491,10 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AK93" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AL93" t="n">
         <v>364</v>
@@ -13565,16 +13565,16 @@
         <v>13</v>
       </c>
       <c r="N94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="O94" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -13589,28 +13589,28 @@
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Y94" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="Z94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="AA94" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AB94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -13625,16 +13625,16 @@
         <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AK94" t="n">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="AL94" t="n">
         <v>437</v>
@@ -13705,19 +13705,19 @@
         <v>5</v>
       </c>
       <c r="N95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="O95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="P95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -13735,25 +13735,25 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Y95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Z95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AA95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="AB95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AC95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AD95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -13771,10 +13771,10 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AK95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="AL95" t="n">
         <v>472</v>
@@ -13845,19 +13845,19 @@
         <v>11</v>
       </c>
       <c r="N96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="O96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="P96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -13875,25 +13875,25 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Y96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="Z96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AA96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AB96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -13911,10 +13911,10 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AK96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AL96" t="n">
         <v>340</v>
@@ -13985,16 +13985,16 @@
         <v>5</v>
       </c>
       <c r="N97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="O97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="P97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="Q97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -14009,28 +14009,28 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W97" t="n">
         <v>1</v>
       </c>
       <c r="X97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="Y97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="Z97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AA97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AB97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AC97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -14045,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI97" t="n">
         <v>1</v>
       </c>
       <c r="AJ97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="AK97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AL97" t="n">
         <v>316</v>
@@ -14125,16 +14125,16 @@
         <v>2</v>
       </c>
       <c r="N98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="O98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
         <v>5</v>
@@ -14158,19 +14158,19 @@
         <v>450</v>
       </c>
       <c r="Y98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="Z98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AA98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AB98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AD98" t="n">
         <v>5</v>
@@ -14194,7 +14194,7 @@
         <v>450</v>
       </c>
       <c r="AK98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AL98" t="n">
         <v>422</v>
@@ -14265,10 +14265,10 @@
         <v>4</v>
       </c>
       <c r="N99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="P99" t="n">
         <v>3</v>
@@ -14277,7 +14277,7 @@
         <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -14289,22 +14289,22 @@
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Y99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Z99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AB99" t="n">
         <v>3</v>
@@ -14313,7 +14313,7 @@
         <v>5</v>
       </c>
       <c r="AD99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -14325,16 +14325,16 @@
         <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AK99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AL99" t="n">
         <v>391</v>
@@ -14405,19 +14405,19 @@
         <v>9</v>
       </c>
       <c r="N100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="O100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="P100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -14435,25 +14435,25 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="Y100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="Z100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AA100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="AB100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -14471,10 +14471,10 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AK100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="AL100" t="n">
         <v>366</v>
@@ -14545,13 +14545,13 @@
         <v>5</v>
       </c>
       <c r="N101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="O101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="P101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -14569,25 +14569,25 @@
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W101" t="n">
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Y101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="Z101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="AA101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="AB101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -14605,16 +14605,16 @@
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AK101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="AL101" t="n">
         <v>335</v>
@@ -14685,22 +14685,22 @@
         <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="O102" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
         <v>0</v>
@@ -14709,34 +14709,34 @@
         <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W102" t="n">
         <v>1</v>
       </c>
       <c r="X102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="Y102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="Z102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="AA102" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
         <v>0</v>
@@ -14745,16 +14745,16 @@
         <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AI102" t="n">
         <v>1</v>
       </c>
       <c r="AJ102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AK102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="AL102" t="n">
         <v>398</v>
@@ -14825,19 +14825,19 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="O103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="P103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -14849,25 +14849,25 @@
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Y103" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Z103" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="AA103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AB103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -14885,16 +14885,16 @@
         <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AK103" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="AL103" t="n">
         <v>322</v>
@@ -14965,19 +14965,19 @@
         <v>6</v>
       </c>
       <c r="N104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="O104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -14989,31 +14989,31 @@
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W104" t="n">
         <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Y104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="Z104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AA104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AB104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -15025,16 +15025,16 @@
         <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AK104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AL104" t="n">
         <v>288</v>
@@ -15105,13 +15105,13 @@
         <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="P105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="n">
         <v>2</v>
@@ -15135,19 +15135,19 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Y105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Z105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AA105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AB105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC105" t="n">
         <v>2</v>
@@ -15171,10 +15171,10 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AK105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AL105" t="n">
         <v>294</v>
@@ -15245,13 +15245,13 @@
         <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="O106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -15260,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -15278,16 +15278,16 @@
         <v>422</v>
       </c>
       <c r="Y106" t="n">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="Z106" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="AA106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="AB106" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -15296,10 +15296,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>422</v>
       </c>
       <c r="AK106" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="AL106" t="n">
         <v>403</v>
@@ -15385,16 +15385,16 @@
         <v>9</v>
       </c>
       <c r="N107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R107" t="n">
         <v>1</v>
@@ -15409,7 +15409,7 @@
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="W107" t="n">
         <v>0</v>
@@ -15418,19 +15418,19 @@
         <v>481</v>
       </c>
       <c r="Y107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AA107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AB107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD107" t="n">
         <v>1</v>
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>481</v>
       </c>
       <c r="AK107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL107" t="n">
         <v>432</v>
@@ -15525,19 +15525,19 @@
         <v>12</v>
       </c>
       <c r="N108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="O108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="P108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -15555,25 +15555,25 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Y108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="Z108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="AA108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="AB108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AK108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="AL108" t="n">
         <v>362</v>
@@ -15665,13 +15665,13 @@
         <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="O109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -15695,19 +15695,19 @@
         <v>4</v>
       </c>
       <c r="X109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="Y109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="Z109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AA109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -15731,10 +15731,10 @@
         <v>4</v>
       </c>
       <c r="AJ109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AK109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="AL109" t="n">
         <v>412</v>
@@ -15945,16 +15945,16 @@
         <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="O111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="P111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -15975,22 +15975,22 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="Y111" t="n">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="Z111" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="AA111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="AB111" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -16011,10 +16011,10 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AK111" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="AL111" t="n">
         <v>255</v>
@@ -16085,19 +16085,19 @@
         <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="O112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="P112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -16109,31 +16109,31 @@
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="W112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="Y112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="Z112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AA112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AB112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -16145,16 +16145,16 @@
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AI112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AK112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="AL112" t="n">
         <v>382</v>
@@ -16225,19 +16225,19 @@
         <v>8</v>
       </c>
       <c r="N113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="O113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -16255,25 +16255,25 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="Y113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Z113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="AA113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -16291,10 +16291,10 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AK113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AL113" t="n">
         <v>420</v>
@@ -16365,19 +16365,19 @@
         <v>6</v>
       </c>
       <c r="N114" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="O114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="P114" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -16395,25 +16395,25 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Y114" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="Z114" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AA114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="AB114" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -16431,10 +16431,10 @@
         <v>0</v>
       </c>
       <c r="AJ114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AK114" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AL114" t="n">
         <v>333</v>
@@ -16505,19 +16505,19 @@
         <v>5</v>
       </c>
       <c r="N115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="O115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="P115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -16538,22 +16538,22 @@
         <v>417</v>
       </c>
       <c r="Y115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="Z115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="AA115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="AB115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
         <v>417</v>
       </c>
       <c r="AK115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AL115" t="n">
         <v>364</v>
@@ -16645,19 +16645,19 @@
         <v>4</v>
       </c>
       <c r="N116" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="O116" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="P116" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -16669,34 +16669,34 @@
         <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W116" t="n">
         <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="Y116" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="Z116" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="AA116" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="AB116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD116" t="n">
         <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
         <v>0</v>
@@ -16705,16 +16705,16 @@
         <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
       </c>
       <c r="AJ116" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="AK116" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AL116" t="n">
         <v>378</v>
@@ -16785,13 +16785,13 @@
         <v>2</v>
       </c>
       <c r="N117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="O117" t="n">
         <v>178</v>
       </c>
       <c r="P117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -16818,16 +16818,16 @@
         <v>462</v>
       </c>
       <c r="Y117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="Z117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="AA117" t="n">
         <v>178</v>
       </c>
       <c r="AB117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -16854,7 +16854,7 @@
         <v>462</v>
       </c>
       <c r="AK117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AL117" t="n">
         <v>420</v>
@@ -16925,16 +16925,16 @@
         <v>6</v>
       </c>
       <c r="N118" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="O118" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P118" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="Q118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R118" t="n">
         <v>1</v>
@@ -16955,25 +16955,25 @@
         <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="Y118" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="Z118" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AA118" t="n">
         <v>138</v>
       </c>
       <c r="AB118" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="AC118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD118" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -16991,10 +16991,10 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AK118" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AL118" t="n">
         <v>336</v>
@@ -17065,13 +17065,13 @@
         <v>11</v>
       </c>
       <c r="N119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="P119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -17095,19 +17095,19 @@
         <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Y119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Z119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AA119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="AB119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -17131,10 +17131,10 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AK119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AL119" t="n">
         <v>344</v>
@@ -17205,19 +17205,19 @@
         <v>22</v>
       </c>
       <c r="N120" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="O120" t="n">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="P120" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -17229,31 +17229,31 @@
         <v>0</v>
       </c>
       <c r="V120" t="n">
+        <v>15</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>364</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>137</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>341</v>
+      </c>
+      <c r="AB120" t="n">
         <v>7</v>
       </c>
-      <c r="W120" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" t="n">
-        <v>488</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>344</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>144</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>318</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>18</v>
-      </c>
       <c r="AC120" t="n">
         <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -17265,16 +17265,16 @@
         <v>0</v>
       </c>
       <c r="AH120" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AK120" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="AL120" t="n">
         <v>353</v>
@@ -17345,13 +17345,13 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="O121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="P121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -17375,19 +17375,19 @@
         <v>1</v>
       </c>
       <c r="X121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Y121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Z121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AA121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AB121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -17411,10 +17411,10 @@
         <v>1</v>
       </c>
       <c r="AJ121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AK121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AL121" t="n">
         <v>321</v>
@@ -17485,13 +17485,13 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="O122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="P122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -17515,16 +17515,16 @@
         <v>1</v>
       </c>
       <c r="X122" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Y122" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Z122" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AA122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="AB122" t="n">
         <v>0</v>
@@ -17551,10 +17551,10 @@
         <v>1</v>
       </c>
       <c r="AJ122" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AK122" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="AL122" t="n">
         <v>297</v>
@@ -17625,19 +17625,19 @@
         <v>2</v>
       </c>
       <c r="N123" t="n">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="O123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="P123" t="n">
         <v>4</v>
       </c>
       <c r="Q123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -17655,25 +17655,25 @@
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="Y123" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="Z123" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="AA123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="AB123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -17691,10 +17691,10 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AK123" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AL123" t="n">
         <v>367</v>
@@ -17765,16 +17765,16 @@
         <v>4</v>
       </c>
       <c r="N124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="O124" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="P124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q124" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R124" t="n">
         <v>0</v>
@@ -17795,22 +17795,22 @@
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="Y124" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="Z124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="AA124" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AB124" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC124" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -17831,10 +17831,10 @@
         <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="AK124" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AL124" t="n">
         <v>410</v>
@@ -17905,22 +17905,22 @@
         <v>4</v>
       </c>
       <c r="N125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
         <v>0</v>
@@ -17929,34 +17929,34 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
       </c>
       <c r="X125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="Y125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="Z125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AA125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AB125" t="n">
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AD125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
         <v>0</v>
@@ -17965,16 +17965,16 @@
         <v>0</v>
       </c>
       <c r="AH125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AI125" t="n">
         <v>0</v>
       </c>
       <c r="AJ125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="AK125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="AL125" t="n">
         <v>394</v>
@@ -18045,13 +18045,13 @@
         <v>15</v>
       </c>
       <c r="N126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="P126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -18075,19 +18075,19 @@
         <v>0</v>
       </c>
       <c r="X126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Y126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="Z126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="AA126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="AB126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -18111,10 +18111,10 @@
         <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AK126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AL126" t="n">
         <v>324</v>
@@ -18185,19 +18185,19 @@
         <v>7</v>
       </c>
       <c r="N127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="O127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="P127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -18215,25 +18215,25 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="Y127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="Z127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AA127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="AB127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -18251,10 +18251,10 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AK127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AL127" t="n">
         <v>384</v>
@@ -18325,50 +18325,50 @@
         <v>7</v>
       </c>
       <c r="N128" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="O128" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="P128" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>17</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>494</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>261</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>233</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>236</v>
+      </c>
+      <c r="AB128" t="n">
         <v>8</v>
       </c>
-      <c r="S128" t="n">
-        <v>9</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>492</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>240</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>246</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>7</v>
-      </c>
       <c r="AC128" t="n">
         <v>0</v>
       </c>
@@ -18385,16 +18385,16 @@
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
       </c>
       <c r="AJ128" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AK128" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="AL128" t="n">
         <v>457</v>
@@ -18465,17 +18465,17 @@
         <v>6</v>
       </c>
       <c r="N129" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="O129" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="P129" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q129" t="n">
         <v>7</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -18489,28 +18489,28 @@
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="Y129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="Z129" t="n">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="AA129" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="AB129" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -18525,16 +18525,16 @@
         <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AI129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="AK129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AL129" t="n">
         <v>429</v>
@@ -18605,13 +18605,13 @@
         <v>1</v>
       </c>
       <c r="N130" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="O130" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="P130" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -18635,19 +18635,19 @@
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Y130" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="Z130" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AA130" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -18671,10 +18671,10 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AK130" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AL130" t="n">
         <v>313</v>
@@ -18745,19 +18745,19 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="O131" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="P131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -18775,16 +18775,16 @@
         <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Y131" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="Z131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AA131" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -18793,7 +18793,7 @@
         <v>1</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -18811,10 +18811,10 @@
         <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AK131" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AL131" t="n">
         <v>324</v>
@@ -18885,19 +18885,19 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="O132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="P132" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q132" t="n">
         <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -18915,25 +18915,25 @@
         <v>0</v>
       </c>
       <c r="X132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Y132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="Z132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AA132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="AB132" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC132" t="n">
         <v>2</v>
       </c>
       <c r="AD132" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -18951,10 +18951,10 @@
         <v>0</v>
       </c>
       <c r="AJ132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AL132" t="n">
         <v>377</v>
@@ -19025,16 +19025,16 @@
         <v>2</v>
       </c>
       <c r="N133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="O133" t="n">
         <v>163</v>
       </c>
       <c r="P133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="Q133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -19055,22 +19055,22 @@
         <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Z133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="AA133" t="n">
         <v>163</v>
       </c>
       <c r="AB133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="AC133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -19091,10 +19091,10 @@
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AK133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="AL133" t="n">
         <v>386</v>
@@ -19165,16 +19165,16 @@
         <v>4</v>
       </c>
       <c r="N134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="O134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="P134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q134" t="n">
         <v>5</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>1</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -19198,19 +19198,19 @@
         <v>398</v>
       </c>
       <c r="Y134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="Z134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AA134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="AB134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC134" t="n">
         <v>5</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -19234,7 +19234,7 @@
         <v>398</v>
       </c>
       <c r="AK134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AL134" t="n">
         <v>370</v>
@@ -19305,31 +19305,31 @@
         <v>7</v>
       </c>
       <c r="N135" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="O135" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="P135" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
         <v>12</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>2</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>5</v>
       </c>
       <c r="W135" t="n">
         <v>0</v>
@@ -19338,19 +19338,19 @@
         <v>414</v>
       </c>
       <c r="Y135" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="Z135" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="AA135" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AB135" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -19374,7 +19374,7 @@
         <v>414</v>
       </c>
       <c r="AK135" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="AL135" t="n">
         <v>368</v>
